--- a/SGC-CKN/Excel/3a8d9bc5-ed94-4351-b90f-4648bba617f3_Lô_CT-02_P1-112_D800_24-03-2026.xlsx
+++ b/SGC-CKN/Excel/3a8d9bc5-ed94-4351-b90f-4648bba617f3_Lô_CT-02_P1-112_D800_24-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P1-112</t>
+    <t>P11-112</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
